--- a/Elemental_properties.xlsx
+++ b/Elemental_properties.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amannodi/Desktop/Purdue_Work/Courses/My_course_Spring25/HW Assignments/HW6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C704A5F7-70DF-A243-AD51-79727271C6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACD1B64-399B-9043-9D6A-0A47F1395B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26360" activeTab="1" xr2:uid="{49B6CDAE-E434-A841-BFB2-E0E281547CEE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{49B6CDAE-E434-A841-BFB2-E0E281547CEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
